--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96FF104-7B01-4746-BE17-31F9FB75251A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E6A98D-7F68-469A-B8CB-C391D4089507}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,13 +86,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -379,235 +379,248 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="2"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4">
+      <c r="G3" s="2"/>
+      <c r="H3" s="3">
         <v>0.75770400000000004</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3">
+      <c r="I3" s="3"/>
+      <c r="J3" s="2">
         <v>-0.18261050571644399</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
         <v>0.41612008162507602</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
+        <v>-5.78075137765727E-2</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2">
+        <v>1.3597531358536001E-2</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
+  <mergeCells count="65">
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -620,27 +633,34 @@
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E6A98D-7F68-469A-B8CB-C391D4089507}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B1C11-0433-4E1F-85C5-741C8AAF8741}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -379,26 +379,26 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
@@ -413,10 +413,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>0.75770400000000004</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="4"/>
       <c r="J3" s="2">
         <v>-0.18261050571644399</v>
       </c>
@@ -463,19 +463,29 @@
         <v>1.3597531358536001E-2</v>
       </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2">
+        <v>-0.143717845796831</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2">
+        <v>0.50647456425735604</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B1C11-0433-4E1F-85C5-741C8AAF8741}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F595DF31-0D24-42CF-A4CF-16A81739709E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -401,10 +401,10 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="3"/>
       <c r="D3" s="2">
         <v>1</v>
       </c>
@@ -423,10 +423,10 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="2">
         <v>1</v>
       </c>
@@ -447,10 +447,10 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="2">
         <v>0</v>
       </c>
@@ -471,10 +471,10 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="2">
         <v>1</v>
       </c>
@@ -487,19 +487,29 @@
         <v>0.50647456425735604</v>
       </c>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2">
+        <v>-7.3994526690530305E-2</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="2">
+        <v>9.9375183154333205E-2</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2">
+        <v>0.373510784555315</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -606,55 +616,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -671,6 +632,55 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F595DF31-0D24-42CF-A4CF-16A81739709E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96025F5A-9DEC-4F1E-A1F5-4FE65C376CDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,10 +495,10 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="2">
         <v>1</v>
       </c>
@@ -511,19 +511,29 @@
         <v>0.373510784555315</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2">
+        <v>-7.9249560954606293E-2</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2">
+        <v>8.2943668587625904E-2</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -616,6 +626,55 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -632,55 +691,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96025F5A-9DEC-4F1E-A1F5-4FE65C376CDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA072E0-C5DD-4B69-9046-763668E98768}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -519,10 +519,10 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="2">
         <v>1</v>
       </c>
@@ -626,55 +626,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -691,6 +642,55 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA072E0-C5DD-4B69-9046-763668E98768}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B820248-F782-4EC7-9532-2F9F56F6EE7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -535,19 +535,29 @@
         <v>8.2943668587625904E-2</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2">
+        <v>-7.5158580678400005E-2</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2">
+        <v>0.33774569202975302</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>0.89389558756481602</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2">
+        <v>0.36332450246375098</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -626,6 +636,55 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -642,55 +701,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B820248-F782-4EC7-9532-2F9F56F6EE7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9507FA00-3DAD-42AA-93F9-7467782F0EF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -376,9 +376,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -400,7 +400,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -422,7 +422,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -446,7 +446,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -518,7 +518,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -542,11 +542,11 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="2">
         <v>0.33774569202975302</v>
       </c>
@@ -559,28 +559,40 @@
         <v>0.36332450246375098</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2">
+        <v>-4.9661978080035703E-2</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2">
+        <v>0.36502520090588497</v>
+      </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2">
+        <v>0.78620380552862201</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>7.0650864049808207E-2</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="3">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -592,7 +604,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -606,7 +618,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -620,7 +632,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -636,55 +648,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -701,6 +664,55 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9507FA00-3DAD-42AA-93F9-7467782F0EF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABED7D86-8EBB-49AE-A253-DF9213FF38B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -376,9 +376,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -400,7 +400,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -422,7 +422,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -446,7 +446,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -518,7 +518,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -542,7 +542,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -566,7 +566,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -583,28 +583,36 @@
         <v>7.0650864049808207E-2</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2">
+        <v>-4.5975298933398398E-2</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>9</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2">
+        <v>0.54019698158248797</v>
+      </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2">
+        <v>0.54267650802453304</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>0.33033871053473002</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -618,7 +626,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -632,7 +640,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABED7D86-8EBB-49AE-A253-DF9213FF38B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984C0810-F4D3-4B4A-8DD5-AC55DCEE2909}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -376,9 +376,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -400,7 +400,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -422,7 +422,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -446,7 +446,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -518,7 +518,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -542,7 +542,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -566,7 +566,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -590,7 +590,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -607,26 +607,36 @@
         <v>0.33033871053473002</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="J11" s="2">
+        <v>-4.10548692742152E-2</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2">
+        <v>0.49694578928321298</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2">
+        <v>0.51261543375697405</v>
+      </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>0.41775657375006903</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -640,7 +650,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -656,6 +666,55 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -672,55 +731,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984C0810-F4D3-4B4A-8DD5-AC55DCEE2909}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B9BF1-E1EE-4B9C-86FD-7F79F83DC0C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -376,9 +376,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:M14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -400,7 +400,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -414,7 +414,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="4">
-        <v>0.75770400000000004</v>
+        <v>0.75770490649881705</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="2">
@@ -422,7 +422,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2</v>
       </c>
@@ -446,7 +446,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>3</v>
       </c>
@@ -470,7 +470,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>5</v>
       </c>
@@ -518,7 +518,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>6</v>
       </c>
@@ -542,7 +542,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>7</v>
       </c>
@@ -566,7 +566,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>8</v>
       </c>
@@ -590,7 +590,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>9</v>
       </c>
@@ -614,7 +614,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>10</v>
       </c>
@@ -631,26 +631,36 @@
         <v>0.41775657375006903</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2">
+        <v>-5.3136364048777104E-3</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2">
+        <v>0.50657956619927103</v>
+      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2">
+        <v>0.54385735347629505</v>
+      </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2">
+        <v>0.42761617038453398</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -666,55 +676,6 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -731,6 +692,55 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Function 3/evals.xlsx
+++ b/Function 3/evals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prithvi\Desktop\Imperial Course\Capstone-Project\Function 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B9BF1-E1EE-4B9C-86FD-7F79F83DC0C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2614BE2A-E716-46E0-B7A5-626EC71658D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M14"/>
+  <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
@@ -655,27 +655,103 @@
         <v>0.42761617038453398</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="J13" s="2">
+        <v>-8.8102116725254694E-3</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="3">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2">
+        <v>0.46444085870829799</v>
+      </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2">
+        <v>0.41190666938047799</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2">
+        <v>0.40554623355493702</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="70">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
@@ -692,55 +768,6 @@
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
